--- a/datasets/KinetiQ_Dataset_Latest.xlsx
+++ b/datasets/KinetiQ_Dataset_Latest.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -514,22 +514,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>rep_squat_1_1726760000000</v>
+        <v>rep_arm_curl_1_1791867557238</v>
       </c>
       <c r="B2" t="str">
-        <v>ses_sample_bench_01</v>
+        <v>ses_mv67o7q5_wxk3</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-09-19 21:55:00</v>
+        <v>2026-10-13 04:59:17</v>
       </c>
       <c r="D2">
-        <v>1726760000000</v>
+        <v>1791867557238</v>
       </c>
       <c r="E2" t="str">
-        <v>Squats</v>
+        <v>Bicep Curl</v>
       </c>
       <c r="F2" t="str">
-        <v>squat</v>
+        <v>arm_curl</v>
       </c>
       <c r="G2" t="str">
         <v>MEDIUM</v>
@@ -544,64 +544,64 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="L2">
-        <v>94.2</v>
+        <v>1.2</v>
       </c>
       <c r="M2">
-        <v>162.5</v>
+        <v>4.2</v>
       </c>
       <c r="N2">
-        <v>161</v>
+        <v>36.8</v>
       </c>
       <c r="O2">
-        <v>68.3</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>10.8</v>
+        <v>73.8</v>
       </c>
       <c r="Q2">
-        <v>93.8</v>
+        <v>1.2</v>
       </c>
       <c r="R2">
-        <v>94.6</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>84.1</v>
+        <v>90</v>
       </c>
       <c r="U2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="V2">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>145</v>
+        <v>1.2</v>
       </c>
       <c r="X2">
-        <v>144.2</v>
+        <v>2.6</v>
       </c>
       <c r="Y2">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="Z2">
-        <v>2.8</v>
+        <v>10.6</v>
       </c>
       <c r="AA2">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="AB2">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>24.4</v>
+        <v>0.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -619,27 +619,27 @@
         <v>None</v>
       </c>
       <c r="AJ2">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>rep_squat_2_1726760005000</v>
+        <v>rep_arm_curl_2_1791867560666</v>
       </c>
       <c r="B3" t="str">
-        <v>ses_sample_bench_01</v>
+        <v>ses_mv67o7q5_wxk3</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-09-19 21:55:05</v>
+        <v>2026-10-13 04:59:20</v>
       </c>
       <c r="D3">
-        <v>1726760005000</v>
+        <v>1791867560666</v>
       </c>
       <c r="E3" t="str">
-        <v>Squats</v>
+        <v>Bicep Curl</v>
       </c>
       <c r="F3" t="str">
-        <v>squat</v>
+        <v>arm_curl</v>
       </c>
       <c r="G3" t="str">
         <v>MEDIUM</v>
@@ -648,93 +648,1963 @@
         <v>2</v>
       </c>
       <c r="I3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>75</v>
+      </c>
+      <c r="L3">
+        <v>9.1</v>
+      </c>
+      <c r="M3">
+        <v>9.1</v>
+      </c>
+      <c r="N3">
+        <v>105.1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>65.9</v>
+      </c>
+      <c r="Q3">
+        <v>9.1</v>
+      </c>
+      <c r="R3">
+        <v>9.1</v>
+      </c>
+      <c r="S3">
+        <v>18.5</v>
+      </c>
+      <c r="T3">
+        <v>90</v>
+      </c>
+      <c r="U3">
+        <v>90</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>27.6</v>
+      </c>
+      <c r="X3">
+        <v>9.1</v>
+      </c>
+      <c r="Y3">
+        <v>18.5</v>
+      </c>
+      <c r="Z3">
+        <v>0.8</v>
+      </c>
+      <c r="AA3">
+        <v>0.4</v>
+      </c>
+      <c r="AB3">
+        <v>0.4</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>1</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>rep_arm_curl_3_1791867563581</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ses_mv67o7q5_wxk3</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-10-13 04:59:23</v>
+      </c>
+      <c r="D4">
+        <v>1791867563581</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F4" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G4" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>75</v>
+      </c>
+      <c r="L4">
+        <v>7.9</v>
+      </c>
+      <c r="M4">
+        <v>7.9</v>
+      </c>
+      <c r="N4">
+        <v>103</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>67.1</v>
+      </c>
+      <c r="Q4">
+        <v>7.9</v>
+      </c>
+      <c r="R4">
+        <v>7.9</v>
+      </c>
+      <c r="S4">
+        <v>33.9</v>
+      </c>
+      <c r="T4">
+        <v>90</v>
+      </c>
+      <c r="U4">
+        <v>90</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>7.9</v>
+      </c>
+      <c r="X4">
+        <v>41.8</v>
+      </c>
+      <c r="Y4">
+        <v>33.9</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>0.9</v>
+      </c>
+      <c r="AB4">
+        <v>0.1</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>rep_arm_curl_4_1791867570375</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ses_mv67o7q5_wxk3</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-10-13 04:59:30</v>
+      </c>
+      <c r="D5">
+        <v>1791867570375</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F5" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G5" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>75</v>
+      </c>
+      <c r="L5">
+        <v>9.4</v>
+      </c>
+      <c r="M5">
+        <v>17.6</v>
+      </c>
+      <c r="N5">
+        <v>155.8</v>
+      </c>
+      <c r="O5">
+        <v>8.2</v>
+      </c>
+      <c r="P5">
+        <v>65.6</v>
+      </c>
+      <c r="Q5">
+        <v>9.4</v>
+      </c>
+      <c r="R5">
+        <v>9.4</v>
+      </c>
+      <c r="S5">
+        <v>7.8</v>
+      </c>
+      <c r="T5">
+        <v>90</v>
+      </c>
+      <c r="U5">
+        <v>90</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>17.2</v>
+      </c>
+      <c r="X5">
+        <v>9.4</v>
+      </c>
+      <c r="Y5">
+        <v>7.8</v>
+      </c>
+      <c r="Z5">
+        <v>4.7</v>
+      </c>
+      <c r="AA5">
+        <v>1.9</v>
+      </c>
+      <c r="AB5">
+        <v>2.8</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>1.7</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>rep_arm_curl_1_1791867607613</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-10-13 05:00:07</v>
+      </c>
+      <c r="D6">
+        <v>1791867607613</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F6" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G6" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>75</v>
+      </c>
+      <c r="L6">
+        <v>5.2</v>
+      </c>
+      <c r="M6">
+        <v>6.6</v>
+      </c>
+      <c r="N6">
+        <v>162.2</v>
+      </c>
+      <c r="O6">
+        <v>1.4</v>
+      </c>
+      <c r="P6">
+        <v>69.8</v>
+      </c>
+      <c r="Q6">
+        <v>5.2</v>
+      </c>
+      <c r="R6">
+        <v>5.2</v>
+      </c>
+      <c r="S6">
+        <v>10.3</v>
+      </c>
+      <c r="T6">
+        <v>90</v>
+      </c>
+      <c r="U6">
+        <v>90</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>15.5</v>
+      </c>
+      <c r="X6">
+        <v>5.2</v>
+      </c>
+      <c r="Y6">
+        <v>10.3</v>
+      </c>
+      <c r="Z6">
+        <v>1.1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>0.1</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>1.3</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>rep_arm_curl_1_1791867612788</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2026-10-13 05:00:12</v>
+      </c>
+      <c r="D7">
+        <v>1791867612788</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F7" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G7" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
         <v>FAIL</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>105</v>
-      </c>
-      <c r="L3">
-        <v>118.4</v>
-      </c>
-      <c r="M3">
-        <v>161</v>
-      </c>
-      <c r="N3">
-        <v>159.5</v>
-      </c>
-      <c r="O3">
-        <v>42.6</v>
-      </c>
-      <c r="P3">
-        <v>-13.4</v>
-      </c>
-      <c r="Q3">
-        <v>117.9</v>
-      </c>
-      <c r="R3">
-        <v>118.9</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3">
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>75</v>
+      </c>
+      <c r="L7">
+        <v>77.5</v>
+      </c>
+      <c r="M7">
+        <v>77.5</v>
+      </c>
+      <c r="N7">
+        <v>155.3</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-2.5</v>
+      </c>
+      <c r="Q7">
+        <v>77.5</v>
+      </c>
+      <c r="R7">
+        <v>77.5</v>
+      </c>
+      <c r="S7">
+        <v>78.5</v>
+      </c>
+      <c r="T7">
+        <v>90</v>
+      </c>
+      <c r="U7">
+        <v>90</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>156</v>
+      </c>
+      <c r="X7">
+        <v>77.5</v>
+      </c>
+      <c r="Y7">
+        <v>78.5</v>
+      </c>
+      <c r="Z7">
+        <v>2.6</v>
+      </c>
+      <c r="AA7">
+        <v>1.3</v>
+      </c>
+      <c r="AB7">
+        <v>2.6</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>rep_arm_curl_2_1791867615311</v>
+      </c>
+      <c r="B8" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026-10-13 05:00:15</v>
+      </c>
+      <c r="D8">
+        <v>1791867615311</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F8" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G8" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>75</v>
+      </c>
+      <c r="L8">
+        <v>17.4</v>
+      </c>
+      <c r="M8">
+        <v>48.6</v>
+      </c>
+      <c r="N8">
+        <v>65.7</v>
+      </c>
+      <c r="O8">
+        <v>31.2</v>
+      </c>
+      <c r="P8">
+        <v>57.6</v>
+      </c>
+      <c r="Q8">
+        <v>17.4</v>
+      </c>
+      <c r="R8">
+        <v>17.4</v>
+      </c>
+      <c r="S8">
+        <v>15.9</v>
+      </c>
+      <c r="T8">
+        <v>90</v>
+      </c>
+      <c r="U8">
+        <v>90</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>33.3</v>
+      </c>
+      <c r="X8">
+        <v>17.4</v>
+      </c>
+      <c r="Y8">
+        <v>15.9</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>0.6</v>
+      </c>
+      <c r="AB8">
+        <v>0.4</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>31.2</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>rep_arm_curl_3_1791867620266</v>
+      </c>
+      <c r="B9" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026-10-13 05:00:20</v>
+      </c>
+      <c r="D9">
+        <v>1791867620266</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F9" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G9" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>75</v>
+      </c>
+      <c r="L9">
+        <v>0.2</v>
+      </c>
+      <c r="M9">
+        <v>7.8</v>
+      </c>
+      <c r="N9">
+        <v>134.7</v>
+      </c>
+      <c r="O9">
+        <v>7.6</v>
+      </c>
+      <c r="P9">
+        <v>74.8</v>
+      </c>
+      <c r="Q9">
+        <v>0.2</v>
+      </c>
+      <c r="R9">
+        <v>0.2</v>
+      </c>
+      <c r="S9">
+        <v>0.1</v>
+      </c>
+      <c r="T9">
+        <v>90</v>
+      </c>
+      <c r="U9">
+        <v>90</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.3</v>
+      </c>
+      <c r="X9">
+        <v>0.2</v>
+      </c>
+      <c r="Y9">
+        <v>0.1</v>
+      </c>
+      <c r="Z9">
+        <v>3.2</v>
+      </c>
+      <c r="AA9">
+        <v>3.1</v>
+      </c>
+      <c r="AB9">
+        <v>0.1</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>2.4</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>rep_arm_curl_4_1791867622761</v>
+      </c>
+      <c r="B10" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026-10-13 05:00:22</v>
+      </c>
+      <c r="D10">
+        <v>1791867622761</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F10" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G10" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>75</v>
+      </c>
+      <c r="L10">
+        <v>59</v>
+      </c>
+      <c r="M10">
+        <v>82.3</v>
+      </c>
+      <c r="N10">
+        <v>150.7</v>
+      </c>
+      <c r="O10">
+        <v>23.3</v>
+      </c>
+      <c r="P10">
+        <v>16</v>
+      </c>
+      <c r="Q10">
+        <v>59</v>
+      </c>
+      <c r="R10">
+        <v>59</v>
+      </c>
+      <c r="S10">
+        <v>97.8</v>
+      </c>
+      <c r="T10">
+        <v>90</v>
+      </c>
+      <c r="U10">
+        <v>90</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>59</v>
+      </c>
+      <c r="X10">
+        <v>156.8</v>
+      </c>
+      <c r="Y10">
+        <v>97.8</v>
+      </c>
+      <c r="Z10">
+        <v>0.6</v>
+      </c>
+      <c r="AA10">
+        <v>0.4</v>
+      </c>
+      <c r="AB10">
+        <v>0.1</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>38.8</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>rep_arm_curl_4_1791867625336</v>
+      </c>
+      <c r="B11" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-10-13 05:00:25</v>
+      </c>
+      <c r="D11">
+        <v>1791867625336</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F11" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G11" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>75</v>
+      </c>
+      <c r="L11">
+        <v>93.2</v>
+      </c>
+      <c r="M11">
+        <v>93.2</v>
+      </c>
+      <c r="N11">
+        <v>144.1</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-18.2</v>
+      </c>
+      <c r="Q11">
+        <v>93.2</v>
+      </c>
+      <c r="R11">
+        <v>93.2</v>
+      </c>
+      <c r="S11">
+        <v>70</v>
+      </c>
+      <c r="T11">
+        <v>90</v>
+      </c>
+      <c r="U11">
+        <v>90</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>93.2</v>
+      </c>
+      <c r="X11">
+        <v>163.2</v>
+      </c>
+      <c r="Y11">
+        <v>70</v>
+      </c>
+      <c r="Z11">
+        <v>0.3</v>
+      </c>
+      <c r="AA11">
+        <v>0.1</v>
+      </c>
+      <c r="AB11">
+        <v>0.3</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>rep_arm_curl_5_1791867627827</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-10-13 05:00:27</v>
+      </c>
+      <c r="D12">
+        <v>1791867627827</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F12" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G12" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>75</v>
+      </c>
+      <c r="L12">
+        <v>8.4</v>
+      </c>
+      <c r="M12">
+        <v>21.3</v>
+      </c>
+      <c r="N12">
+        <v>157.5</v>
+      </c>
+      <c r="O12">
+        <v>12.9</v>
+      </c>
+      <c r="P12">
+        <v>66.6</v>
+      </c>
+      <c r="Q12">
+        <v>8.4</v>
+      </c>
+      <c r="R12">
+        <v>8.4</v>
+      </c>
+      <c r="S12">
+        <v>9.5</v>
+      </c>
+      <c r="T12">
+        <v>90</v>
+      </c>
+      <c r="U12">
+        <v>90</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>17.9</v>
+      </c>
+      <c r="X12">
+        <v>8.4</v>
+      </c>
+      <c r="Y12">
+        <v>9.5</v>
+      </c>
+      <c r="Z12">
+        <v>0.6</v>
+      </c>
+      <c r="AA12">
+        <v>0.5</v>
+      </c>
+      <c r="AB12">
+        <v>0.1</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>21.5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>rep_arm_curl_6_1791867631720</v>
+      </c>
+      <c r="B13" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-10-13 05:00:31</v>
+      </c>
+      <c r="D13">
+        <v>1791867631720</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F13" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G13" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>75</v>
+      </c>
+      <c r="L13">
+        <v>3.7</v>
+      </c>
+      <c r="M13">
+        <v>48.4</v>
+      </c>
+      <c r="N13">
+        <v>37.7</v>
+      </c>
+      <c r="O13">
+        <v>44.7</v>
+      </c>
+      <c r="P13">
+        <v>71.3</v>
+      </c>
+      <c r="Q13">
+        <v>3.7</v>
+      </c>
+      <c r="R13">
+        <v>3.7</v>
+      </c>
+      <c r="S13">
+        <v>6.2</v>
+      </c>
+      <c r="T13">
+        <v>90</v>
+      </c>
+      <c r="U13">
+        <v>90</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>3.7</v>
+      </c>
+      <c r="X13">
+        <v>9.9</v>
+      </c>
+      <c r="Y13">
+        <v>6.2</v>
+      </c>
+      <c r="Z13">
+        <v>1.9</v>
+      </c>
+      <c r="AA13">
+        <v>1.8</v>
+      </c>
+      <c r="AB13">
+        <v>0.1</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>23.5</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>rep_arm_curl_7_1791867634639</v>
+      </c>
+      <c r="B14" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-10-13 05:00:34</v>
+      </c>
+      <c r="D14">
+        <v>1791867634639</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F14" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G14" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H14">
+        <v>7</v>
+      </c>
+      <c r="I14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>75</v>
+      </c>
+      <c r="L14">
+        <v>15.4</v>
+      </c>
+      <c r="M14">
+        <v>76.7</v>
+      </c>
+      <c r="N14">
+        <v>75.3</v>
+      </c>
+      <c r="O14">
+        <v>61.3</v>
+      </c>
+      <c r="P14">
+        <v>59.6</v>
+      </c>
+      <c r="Q14">
+        <v>15.4</v>
+      </c>
+      <c r="R14">
+        <v>15.4</v>
+      </c>
+      <c r="S14">
+        <v>58</v>
+      </c>
+      <c r="T14">
+        <v>90</v>
+      </c>
+      <c r="U14">
+        <v>90</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>73.4</v>
+      </c>
+      <c r="X14">
+        <v>15.4</v>
+      </c>
+      <c r="Y14">
+        <v>58</v>
+      </c>
+      <c r="Z14">
+        <v>0.6</v>
+      </c>
+      <c r="AA14">
+        <v>0.3</v>
+      </c>
+      <c r="AB14">
+        <v>0.3</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>102.2</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ14">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>rep_arm_curl_8_1791867640853</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-10-13 05:00:40</v>
+      </c>
+      <c r="D15">
+        <v>1791867640853</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F15" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G15" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H15">
+        <v>8</v>
+      </c>
+      <c r="I15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>75</v>
+      </c>
+      <c r="L15">
+        <v>6.3</v>
+      </c>
+      <c r="M15">
+        <v>8.2</v>
+      </c>
+      <c r="N15">
+        <v>164</v>
+      </c>
+      <c r="O15">
+        <v>1.9</v>
+      </c>
+      <c r="P15">
+        <v>68.7</v>
+      </c>
+      <c r="Q15">
+        <v>6.3</v>
+      </c>
+      <c r="R15">
+        <v>6.3</v>
+      </c>
+      <c r="S15">
+        <v>10.3</v>
+      </c>
+      <c r="T15">
+        <v>90</v>
+      </c>
+      <c r="U15">
+        <v>90</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>16.6</v>
+      </c>
+      <c r="X15">
+        <v>6.3</v>
+      </c>
+      <c r="Y15">
+        <v>10.3</v>
+      </c>
+      <c r="Z15">
+        <v>2.5</v>
+      </c>
+      <c r="AA15">
+        <v>2.3</v>
+      </c>
+      <c r="AB15">
+        <v>0.2</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0.8</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>rep_arm_curl_8_1791867642486</v>
+      </c>
+      <c r="B16" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-10-13 05:00:42</v>
+      </c>
+      <c r="D16">
+        <v>1791867642486</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F16" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G16" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+      <c r="I16" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>75</v>
+      </c>
+      <c r="L16">
+        <v>28.3</v>
+      </c>
+      <c r="M16">
+        <v>28.3</v>
+      </c>
+      <c r="N16">
+        <v>136.6</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>46.7</v>
+      </c>
+      <c r="Q16">
+        <v>28.3</v>
+      </c>
+      <c r="R16">
+        <v>28.3</v>
+      </c>
+      <c r="S16">
+        <v>137</v>
+      </c>
+      <c r="T16">
+        <v>90</v>
+      </c>
+      <c r="U16">
+        <v>90</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>28.3</v>
+      </c>
+      <c r="X16">
+        <v>165.3</v>
+      </c>
+      <c r="Y16">
+        <v>137</v>
+      </c>
+      <c r="Z16">
+        <v>0.3</v>
+      </c>
+      <c r="AA16">
+        <v>0.2</v>
+      </c>
+      <c r="AB16">
+        <v>0.3</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>rep_arm_curl_9_1791867650811</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-10-13 05:00:50</v>
+      </c>
+      <c r="D17">
+        <v>1791867650811</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F17" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G17" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H17">
+        <v>9</v>
+      </c>
+      <c r="I17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>75</v>
+      </c>
+      <c r="L17">
+        <v>9.9</v>
+      </c>
+      <c r="M17">
+        <v>33.8</v>
+      </c>
+      <c r="N17">
+        <v>57.3</v>
+      </c>
+      <c r="O17">
+        <v>23.9</v>
+      </c>
+      <c r="P17">
+        <v>65.1</v>
+      </c>
+      <c r="Q17">
+        <v>9.9</v>
+      </c>
+      <c r="R17">
+        <v>9.9</v>
+      </c>
+      <c r="S17">
+        <v>5.6</v>
+      </c>
+      <c r="T17">
+        <v>90</v>
+      </c>
+      <c r="U17">
+        <v>90</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>15.5</v>
+      </c>
+      <c r="X17">
+        <v>9.9</v>
+      </c>
+      <c r="Y17">
+        <v>5.6</v>
+      </c>
+      <c r="Z17">
+        <v>3</v>
+      </c>
+      <c r="AA17">
+        <v>1.1</v>
+      </c>
+      <c r="AB17">
+        <v>1.9</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>8</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>rep_arm_curl_10_1791867658002</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ses_mv67phvo_idie</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-10-13 05:00:58</v>
+      </c>
+      <c r="D18">
+        <v>1791867658002</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F18" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G18" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H18">
+        <v>10</v>
+      </c>
+      <c r="I18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>75</v>
+      </c>
+      <c r="L18">
+        <v>4.3</v>
+      </c>
+      <c r="M18">
+        <v>11.7</v>
+      </c>
+      <c r="N18">
+        <v>166.1</v>
+      </c>
+      <c r="O18">
+        <v>7.4</v>
+      </c>
+      <c r="P18">
+        <v>70.7</v>
+      </c>
+      <c r="Q18">
+        <v>4.3</v>
+      </c>
+      <c r="R18">
+        <v>4.3</v>
+      </c>
+      <c r="S18">
+        <v>4</v>
+      </c>
+      <c r="T18">
+        <v>90</v>
+      </c>
+      <c r="U18">
+        <v>90</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>4.3</v>
+      </c>
+      <c r="X18">
+        <v>8.3</v>
+      </c>
+      <c r="Y18">
+        <v>4</v>
+      </c>
+      <c r="Z18">
+        <v>5.4</v>
+      </c>
+      <c r="AA18">
+        <v>5.2</v>
+      </c>
+      <c r="AB18">
+        <v>0.1</v>
+      </c>
+      <c r="AC18">
+        <v>5.2</v>
+      </c>
+      <c r="AD18">
+        <v>1.4</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>rep_arm_curl_1_1791868375341</v>
+      </c>
+      <c r="B19" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-10-13 05:12:55</v>
+      </c>
+      <c r="D19">
+        <v>1791868375341</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F19" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G19" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>75</v>
+      </c>
+      <c r="L19">
+        <v>31.1</v>
+      </c>
+      <c r="M19">
+        <v>44.3</v>
+      </c>
+      <c r="N19">
+        <v>151.1</v>
+      </c>
+      <c r="O19">
+        <v>13.2</v>
+      </c>
+      <c r="P19">
+        <v>43.9</v>
+      </c>
+      <c r="Q19">
+        <v>31.1</v>
+      </c>
+      <c r="R19">
+        <v>31.1</v>
+      </c>
+      <c r="S19">
+        <v>104.6</v>
+      </c>
+      <c r="T19">
+        <v>90</v>
+      </c>
+      <c r="U19">
+        <v>90</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>31.1</v>
+      </c>
+      <c r="X19">
+        <v>135.7</v>
+      </c>
+      <c r="Y19">
+        <v>104.6</v>
+      </c>
+      <c r="Z19">
+        <v>1.9</v>
+      </c>
+      <c r="AA19">
+        <v>1.7</v>
+      </c>
+      <c r="AB19">
+        <v>0.1</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>6.9</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ19">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>rep_arm_curl_2_1791868381624</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-10-13 05:13:01</v>
+      </c>
+      <c r="D20">
+        <v>1791868381624</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Bicep Curl</v>
+      </c>
+      <c r="F20" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="G20" t="str">
+        <v>MEDIUM</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>75</v>
+      </c>
+      <c r="L20">
+        <v>33.3</v>
+      </c>
+      <c r="M20">
         <v>105.2</v>
       </c>
-      <c r="U3">
-        <v>106.1</v>
-      </c>
-      <c r="V3">
-        <v>22</v>
-      </c>
-      <c r="W3">
-        <v>143</v>
-      </c>
-      <c r="X3">
-        <v>142.5</v>
-      </c>
-      <c r="Y3">
-        <v>0.5</v>
-      </c>
-      <c r="Z3">
-        <v>2.1</v>
-      </c>
-      <c r="AA3">
-        <v>1.1</v>
-      </c>
-      <c r="AB3">
-        <v>1</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>20.3</v>
-      </c>
-      <c r="AE3">
-        <v>1</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="str">
-        <v>Insufficient depth (118.4° reached, &lt;=105.0° required)</v>
-      </c>
-      <c r="AJ3">
-        <v>45</v>
+      <c r="N20">
+        <v>156.7</v>
+      </c>
+      <c r="O20">
+        <v>71.9</v>
+      </c>
+      <c r="P20">
+        <v>41.7</v>
+      </c>
+      <c r="Q20">
+        <v>33.3</v>
+      </c>
+      <c r="R20">
+        <v>33.3</v>
+      </c>
+      <c r="S20">
+        <v>116.9</v>
+      </c>
+      <c r="T20">
+        <v>90</v>
+      </c>
+      <c r="U20">
+        <v>90</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>33.3</v>
+      </c>
+      <c r="X20">
+        <v>150.2</v>
+      </c>
+      <c r="Y20">
+        <v>116.9</v>
+      </c>
+      <c r="Z20">
+        <v>1.8</v>
+      </c>
+      <c r="AA20">
+        <v>1.7</v>
+      </c>
+      <c r="AB20">
+        <v>0.1</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>39.9</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>1</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="str">
+        <v>None</v>
+      </c>
+      <c r="AJ20">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AJ3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -804,16 +2674,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ses_sample_bench_01</v>
+        <v>ses_mv67phvo_idie</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-19 21:55:00</v>
+        <v>2026-10-13 05:00:59</v>
       </c>
       <c r="C2" t="str">
-        <v>Squats</v>
+        <v>Bicep Curl</v>
       </c>
       <c r="D2" t="str">
-        <v>squat</v>
+        <v>arm_curl</v>
       </c>
       <c r="E2" t="str">
         <v>MEDIUM</v>
@@ -822,43 +2692,43 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
+        <v>77</v>
+      </c>
+      <c r="M2">
+        <v>93</v>
+      </c>
+      <c r="N2">
         <v>50</v>
       </c>
-      <c r="M2">
-        <v>72</v>
-      </c>
-      <c r="N2">
-        <v>32</v>
-      </c>
       <c r="O2">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="P2">
-        <v>106.3</v>
+        <v>25.3</v>
       </c>
       <c r="Q2">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.9</v>
+        <v>38.7</v>
       </c>
       <c r="S2" t="str">
-        <v>Insufficient depth</v>
+        <v>None</v>
       </c>
     </row>
   </sheetData>
@@ -870,7 +2740,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -927,46 +2797,46 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-19 21:55:00.120</v>
+        <v>2026-10-13 05:12:47.370</v>
       </c>
       <c r="C2">
-        <v>0.12</v>
+        <v>2.78</v>
       </c>
       <c r="D2" t="str">
-        <v>ses_sample_bench_01</v>
+        <v>ses_mv685qul_9ygn</v>
       </c>
       <c r="E2" t="str">
         <v>squat</v>
       </c>
       <c r="F2" t="str">
-        <v>READY</v>
+        <v>IDLE</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H2">
-        <v>162.5</v>
+        <v>177.3</v>
       </c>
       <c r="I2">
-        <v>163</v>
+        <v>179.5</v>
       </c>
       <c r="J2">
-        <v>162.8</v>
+        <v>178.4</v>
       </c>
       <c r="K2">
-        <v>168</v>
+        <v>179.4</v>
       </c>
       <c r="L2">
-        <v>168.5</v>
+        <v>172.8</v>
       </c>
       <c r="M2">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="N2">
-        <v>145</v>
+        <v>6.1</v>
       </c>
       <c r="O2">
-        <v>144.2</v>
+        <v>163.2</v>
       </c>
       <c r="P2">
         <v>0.99</v>
@@ -977,61 +2847,2461 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-19 21:55:01.320</v>
+        <v>2026-10-13 05:12:47.653</v>
       </c>
       <c r="C3">
-        <v>1.32</v>
+        <v>3.06</v>
       </c>
       <c r="D3" t="str">
-        <v>ses_sample_bench_01</v>
+        <v>ses_mv685qul_9ygn</v>
       </c>
       <c r="E3" t="str">
         <v>squat</v>
       </c>
       <c r="F3" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G3">
+        <v>179</v>
+      </c>
+      <c r="H3">
+        <v>175.4</v>
+      </c>
+      <c r="I3">
+        <v>178.6</v>
+      </c>
+      <c r="J3">
+        <v>177</v>
+      </c>
+      <c r="K3">
+        <v>179.5</v>
+      </c>
+      <c r="L3">
+        <v>172.9</v>
+      </c>
+      <c r="M3">
+        <v>0.5</v>
+      </c>
+      <c r="N3">
+        <v>11.9</v>
+      </c>
+      <c r="O3">
+        <v>166.2</v>
+      </c>
+      <c r="P3">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-10-13 05:12:47.897</v>
+      </c>
+      <c r="C4">
+        <v>3.31</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ses_mv685qul_9ygn</v>
+      </c>
+      <c r="E4" t="str">
+        <v>squat</v>
+      </c>
+      <c r="F4" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G4">
+        <v>178</v>
+      </c>
+      <c r="H4">
+        <v>175.4</v>
+      </c>
+      <c r="I4">
+        <v>177.8</v>
+      </c>
+      <c r="J4">
+        <v>176.6</v>
+      </c>
+      <c r="K4">
+        <v>179.3</v>
+      </c>
+      <c r="L4">
+        <v>174</v>
+      </c>
+      <c r="M4">
+        <v>0.8</v>
+      </c>
+      <c r="N4">
+        <v>12.8</v>
+      </c>
+      <c r="O4">
+        <v>159.8</v>
+      </c>
+      <c r="P4">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-10-13 05:12:48.170</v>
+      </c>
+      <c r="C5">
+        <v>3.58</v>
+      </c>
+      <c r="D5" t="str">
+        <v>ses_mv685qul_9ygn</v>
+      </c>
+      <c r="E5" t="str">
+        <v>squat</v>
+      </c>
+      <c r="F5" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G5">
+        <v>178</v>
+      </c>
+      <c r="H5">
+        <v>177</v>
+      </c>
+      <c r="I5">
+        <v>178.3</v>
+      </c>
+      <c r="J5">
+        <v>177.7</v>
+      </c>
+      <c r="K5">
+        <v>178.9</v>
+      </c>
+      <c r="L5">
+        <v>173.3</v>
+      </c>
+      <c r="M5">
+        <v>0.6</v>
+      </c>
+      <c r="N5">
+        <v>10.2</v>
+      </c>
+      <c r="O5">
+        <v>142.9</v>
+      </c>
+      <c r="P5">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-10-13 05:12:48.414</v>
+      </c>
+      <c r="C6">
+        <v>3.83</v>
+      </c>
+      <c r="D6" t="str">
+        <v>ses_mv685qul_9ygn</v>
+      </c>
+      <c r="E6" t="str">
+        <v>squat</v>
+      </c>
+      <c r="F6" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G6">
+        <v>178</v>
+      </c>
+      <c r="H6">
+        <v>176.3</v>
+      </c>
+      <c r="I6">
+        <v>177.7</v>
+      </c>
+      <c r="J6">
+        <v>177</v>
+      </c>
+      <c r="K6">
+        <v>179.7</v>
+      </c>
+      <c r="L6">
+        <v>173.6</v>
+      </c>
+      <c r="M6">
+        <v>1.5</v>
+      </c>
+      <c r="N6">
+        <v>15.4</v>
+      </c>
+      <c r="O6">
+        <v>143</v>
+      </c>
+      <c r="P6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-10-13 05:12:48.653</v>
+      </c>
+      <c r="C7">
+        <v>4.06</v>
+      </c>
+      <c r="D7" t="str">
+        <v>ses_mv685qul_9ygn</v>
+      </c>
+      <c r="E7" t="str">
+        <v>squat</v>
+      </c>
+      <c r="F7" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G7">
+        <v>179</v>
+      </c>
+      <c r="H7">
+        <v>177</v>
+      </c>
+      <c r="I7">
+        <v>178.6</v>
+      </c>
+      <c r="J7">
+        <v>177.8</v>
+      </c>
+      <c r="K7">
+        <v>178.5</v>
+      </c>
+      <c r="L7">
+        <v>171.8</v>
+      </c>
+      <c r="M7">
+        <v>0.9</v>
+      </c>
+      <c r="N7">
+        <v>15.1</v>
+      </c>
+      <c r="O7">
+        <v>143.7</v>
+      </c>
+      <c r="P7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-10-13 05:12:48.868</v>
+      </c>
+      <c r="C8">
+        <v>4.28</v>
+      </c>
+      <c r="D8" t="str">
+        <v>ses_mv685qul_9ygn</v>
+      </c>
+      <c r="E8" t="str">
+        <v>squat</v>
+      </c>
+      <c r="F8" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G8">
+        <v>180</v>
+      </c>
+      <c r="H8">
+        <v>177.4</v>
+      </c>
+      <c r="I8">
+        <v>179.9</v>
+      </c>
+      <c r="J8">
+        <v>178.7</v>
+      </c>
+      <c r="K8">
+        <v>178.6</v>
+      </c>
+      <c r="L8">
+        <v>171.7</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>10.7</v>
+      </c>
+      <c r="O8">
+        <v>108.8</v>
+      </c>
+      <c r="P8">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-10-13 05:12:49.087</v>
+      </c>
+      <c r="C9">
+        <v>4.5</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ses_mv685qul_9ygn</v>
+      </c>
+      <c r="E9" t="str">
+        <v>squat</v>
+      </c>
+      <c r="F9" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G9">
+        <v>179</v>
+      </c>
+      <c r="H9">
+        <v>176.4</v>
+      </c>
+      <c r="I9">
+        <v>179.1</v>
+      </c>
+      <c r="J9">
+        <v>177.8</v>
+      </c>
+      <c r="K9">
+        <v>179.1</v>
+      </c>
+      <c r="L9">
+        <v>173.7</v>
+      </c>
+      <c r="M9">
+        <v>0.7</v>
+      </c>
+      <c r="N9">
+        <v>10.2</v>
+      </c>
+      <c r="O9">
+        <v>97.2</v>
+      </c>
+      <c r="P9">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-10-13 05:12:49.359</v>
+      </c>
+      <c r="C10">
+        <v>4.77</v>
+      </c>
+      <c r="D10" t="str">
+        <v>ses_mv685qul_9ygn</v>
+      </c>
+      <c r="E10" t="str">
+        <v>squat</v>
+      </c>
+      <c r="F10" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G10">
+        <v>179</v>
+      </c>
+      <c r="H10">
+        <v>177</v>
+      </c>
+      <c r="I10">
+        <v>178.8</v>
+      </c>
+      <c r="J10">
+        <v>177.9</v>
+      </c>
+      <c r="K10">
+        <v>179.3</v>
+      </c>
+      <c r="L10">
+        <v>173.5</v>
+      </c>
+      <c r="M10">
+        <v>0.7</v>
+      </c>
+      <c r="N10">
+        <v>8.5</v>
+      </c>
+      <c r="O10">
+        <v>134.1</v>
+      </c>
+      <c r="P10">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-10-13 05:12:49.586</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="str">
+        <v>ses_mv685qul_9ygn</v>
+      </c>
+      <c r="E11" t="str">
+        <v>squat</v>
+      </c>
+      <c r="F11" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G11">
+        <v>179</v>
+      </c>
+      <c r="H11">
+        <v>176.3</v>
+      </c>
+      <c r="I11">
+        <v>179.4</v>
+      </c>
+      <c r="J11">
+        <v>177.9</v>
+      </c>
+      <c r="K11">
+        <v>177.8</v>
+      </c>
+      <c r="L11">
+        <v>171.4</v>
+      </c>
+      <c r="M11">
+        <v>0.4</v>
+      </c>
+      <c r="N11">
+        <v>10.3</v>
+      </c>
+      <c r="O11">
+        <v>72.8</v>
+      </c>
+      <c r="P11">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-10-13 05:12:51.657</v>
+      </c>
+      <c r="C12">
+        <v>0.01</v>
+      </c>
+      <c r="D12" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E12" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F12" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G12">
+        <v>178</v>
+      </c>
+      <c r="H12">
+        <v>176.4</v>
+      </c>
+      <c r="I12">
+        <v>178.2</v>
+      </c>
+      <c r="J12">
+        <v>177.3</v>
+      </c>
+      <c r="K12">
+        <v>180</v>
+      </c>
+      <c r="L12">
+        <v>173.4</v>
+      </c>
+      <c r="M12">
+        <v>0.6</v>
+      </c>
+      <c r="N12">
+        <v>4.8</v>
+      </c>
+      <c r="O12">
+        <v>147.4</v>
+      </c>
+      <c r="P12">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-10-13 05:12:51.954</v>
+      </c>
+      <c r="C13">
+        <v>0.3</v>
+      </c>
+      <c r="D13" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E13" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F13" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G13">
+        <v>178</v>
+      </c>
+      <c r="H13">
+        <v>176.3</v>
+      </c>
+      <c r="I13">
+        <v>177.9</v>
+      </c>
+      <c r="J13">
+        <v>177.1</v>
+      </c>
+      <c r="K13">
+        <v>179.2</v>
+      </c>
+      <c r="L13">
+        <v>173.2</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>3.1</v>
+      </c>
+      <c r="O13">
+        <v>145.5</v>
+      </c>
+      <c r="P13">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-10-13 05:12:52.223</v>
+      </c>
+      <c r="C14">
+        <v>0.57</v>
+      </c>
+      <c r="D14" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E14" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F14" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G14">
+        <v>177</v>
+      </c>
+      <c r="H14">
+        <v>175.7</v>
+      </c>
+      <c r="I14">
+        <v>176.6</v>
+      </c>
+      <c r="J14">
+        <v>176.1</v>
+      </c>
+      <c r="K14">
+        <v>180</v>
+      </c>
+      <c r="L14">
+        <v>173.9</v>
+      </c>
+      <c r="M14">
+        <v>0.9</v>
+      </c>
+      <c r="N14">
+        <v>3.7</v>
+      </c>
+      <c r="O14">
+        <v>144.4</v>
+      </c>
+      <c r="P14">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-10-13 05:12:52.560</v>
+      </c>
+      <c r="C15">
+        <v>0.91</v>
+      </c>
+      <c r="D15" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E15" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F15" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G15">
+        <v>178</v>
+      </c>
+      <c r="H15">
+        <v>176.6</v>
+      </c>
+      <c r="I15">
+        <v>177.5</v>
+      </c>
+      <c r="J15">
+        <v>177.1</v>
+      </c>
+      <c r="K15">
+        <v>179.1</v>
+      </c>
+      <c r="L15">
+        <v>173.9</v>
+      </c>
+      <c r="M15">
+        <v>0.6</v>
+      </c>
+      <c r="N15">
+        <v>2.8</v>
+      </c>
+      <c r="O15">
+        <v>109.7</v>
+      </c>
+      <c r="P15">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-10-13 05:12:52.792</v>
+      </c>
+      <c r="C16">
+        <v>1.14</v>
+      </c>
+      <c r="D16" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E16" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F16" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G16">
+        <v>179</v>
+      </c>
+      <c r="H16">
+        <v>176.7</v>
+      </c>
+      <c r="I16">
+        <v>179.1</v>
+      </c>
+      <c r="J16">
+        <v>177.9</v>
+      </c>
+      <c r="K16">
+        <v>178.9</v>
+      </c>
+      <c r="L16">
+        <v>173.2</v>
+      </c>
+      <c r="M16">
+        <v>0.8</v>
+      </c>
+      <c r="N16">
+        <v>0.9</v>
+      </c>
+      <c r="O16">
+        <v>135.7</v>
+      </c>
+      <c r="P16">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-10-13 05:12:53.003</v>
+      </c>
+      <c r="C17">
+        <v>1.35</v>
+      </c>
+      <c r="D17" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E17" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F17" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G17">
+        <v>179</v>
+      </c>
+      <c r="H17">
+        <v>176.6</v>
+      </c>
+      <c r="I17">
+        <v>178.8</v>
+      </c>
+      <c r="J17">
+        <v>177.7</v>
+      </c>
+      <c r="K17">
+        <v>179.6</v>
+      </c>
+      <c r="L17">
+        <v>173.6</v>
+      </c>
+      <c r="M17">
+        <v>1.5</v>
+      </c>
+      <c r="N17">
+        <v>13.9</v>
+      </c>
+      <c r="O17">
+        <v>154.1</v>
+      </c>
+      <c r="P17">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>7</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-10-13 05:12:53.257</v>
+      </c>
+      <c r="C18">
+        <v>1.61</v>
+      </c>
+      <c r="D18" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E18" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F18" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G18">
+        <v>179</v>
+      </c>
+      <c r="H18">
+        <v>177.1</v>
+      </c>
+      <c r="I18">
+        <v>178.5</v>
+      </c>
+      <c r="J18">
+        <v>177.8</v>
+      </c>
+      <c r="K18">
+        <v>179.8</v>
+      </c>
+      <c r="L18">
+        <v>173.8</v>
+      </c>
+      <c r="M18">
+        <v>1.4</v>
+      </c>
+      <c r="N18">
+        <v>29.2</v>
+      </c>
+      <c r="O18">
+        <v>169.3</v>
+      </c>
+      <c r="P18">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>8</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-10-13 05:12:53.491</v>
+      </c>
+      <c r="C19">
+        <v>1.84</v>
+      </c>
+      <c r="D19" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E19" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F19" t="str">
+        <v>DESCENDING</v>
+      </c>
+      <c r="G19">
+        <v>178</v>
+      </c>
+      <c r="H19">
+        <v>176.7</v>
+      </c>
+      <c r="I19">
+        <v>177.9</v>
+      </c>
+      <c r="J19">
+        <v>177.3</v>
+      </c>
+      <c r="K19">
+        <v>179.2</v>
+      </c>
+      <c r="L19">
+        <v>173.4</v>
+      </c>
+      <c r="M19">
+        <v>2.7</v>
+      </c>
+      <c r="N19">
+        <v>44.3</v>
+      </c>
+      <c r="O19">
+        <v>158.3</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>9</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-10-13 05:12:53.810</v>
+      </c>
+      <c r="C20">
+        <v>2.16</v>
+      </c>
+      <c r="D20" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E20" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F20" t="str">
         <v>BOTTOM</v>
       </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-      <c r="H3">
-        <v>93.8</v>
-      </c>
-      <c r="I3">
-        <v>94.6</v>
-      </c>
-      <c r="J3">
-        <v>94.2</v>
-      </c>
-      <c r="K3">
-        <v>84.1</v>
-      </c>
-      <c r="L3">
-        <v>85</v>
-      </c>
-      <c r="M3">
-        <v>18.5</v>
-      </c>
-      <c r="N3">
-        <v>146</v>
-      </c>
-      <c r="O3">
-        <v>145.1</v>
-      </c>
-      <c r="P3">
-        <v>0.98</v>
+      <c r="G20">
+        <v>179</v>
+      </c>
+      <c r="H20">
+        <v>176.3</v>
+      </c>
+      <c r="I20">
+        <v>178.7</v>
+      </c>
+      <c r="J20">
+        <v>177.5</v>
+      </c>
+      <c r="K20">
+        <v>176.6</v>
+      </c>
+      <c r="L20">
+        <v>171.9</v>
+      </c>
+      <c r="M20">
+        <v>4.5</v>
+      </c>
+      <c r="N20">
+        <v>50.6</v>
+      </c>
+      <c r="O20">
+        <v>170.6</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-10-13 05:12:54.119</v>
+      </c>
+      <c r="C21">
+        <v>2.47</v>
+      </c>
+      <c r="D21" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E21" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F21" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G21">
+        <v>179</v>
+      </c>
+      <c r="H21">
+        <v>177.2</v>
+      </c>
+      <c r="I21">
+        <v>178.7</v>
+      </c>
+      <c r="J21">
+        <v>178</v>
+      </c>
+      <c r="K21">
+        <v>177.3</v>
+      </c>
+      <c r="L21">
+        <v>172.6</v>
+      </c>
+      <c r="M21">
+        <v>2.1</v>
+      </c>
+      <c r="N21">
+        <v>39.8</v>
+      </c>
+      <c r="O21">
+        <v>165.7</v>
+      </c>
+      <c r="P21">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-10-13 05:12:54.353</v>
+      </c>
+      <c r="C22">
+        <v>2.7</v>
+      </c>
+      <c r="D22" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E22" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F22" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G22">
+        <v>179</v>
+      </c>
+      <c r="H22">
+        <v>177.1</v>
+      </c>
+      <c r="I22">
+        <v>179.3</v>
+      </c>
+      <c r="J22">
+        <v>178.2</v>
+      </c>
+      <c r="K22">
+        <v>177.8</v>
+      </c>
+      <c r="L22">
+        <v>172.6</v>
+      </c>
+      <c r="M22">
+        <v>2.3</v>
+      </c>
+      <c r="N22">
+        <v>36</v>
+      </c>
+      <c r="O22">
+        <v>141.5</v>
+      </c>
+      <c r="P22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>12</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-10-13 05:12:54.599</v>
+      </c>
+      <c r="C23">
+        <v>2.95</v>
+      </c>
+      <c r="D23" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E23" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F23" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G23">
+        <v>179</v>
+      </c>
+      <c r="H23">
+        <v>176.7</v>
+      </c>
+      <c r="I23">
+        <v>179</v>
+      </c>
+      <c r="J23">
+        <v>177.9</v>
+      </c>
+      <c r="K23">
+        <v>177.7</v>
+      </c>
+      <c r="L23">
+        <v>172.3</v>
+      </c>
+      <c r="M23">
+        <v>2.4</v>
+      </c>
+      <c r="N23">
+        <v>31.6</v>
+      </c>
+      <c r="O23">
+        <v>163.3</v>
+      </c>
+      <c r="P23">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>13</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-10-13 05:12:54.843</v>
+      </c>
+      <c r="C24">
+        <v>3.19</v>
+      </c>
+      <c r="D24" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E24" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F24" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G24">
+        <v>179</v>
+      </c>
+      <c r="H24">
+        <v>176.3</v>
+      </c>
+      <c r="I24">
+        <v>178.6</v>
+      </c>
+      <c r="J24">
+        <v>177.5</v>
+      </c>
+      <c r="K24">
+        <v>178.5</v>
+      </c>
+      <c r="L24">
+        <v>173.2</v>
+      </c>
+      <c r="M24">
+        <v>3</v>
+      </c>
+      <c r="N24">
+        <v>32.4</v>
+      </c>
+      <c r="O24">
+        <v>160.2</v>
+      </c>
+      <c r="P24">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>14</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-10-13 05:12:55.092</v>
+      </c>
+      <c r="C25">
+        <v>3.44</v>
+      </c>
+      <c r="D25" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E25" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F25" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G25">
+        <v>179</v>
+      </c>
+      <c r="H25">
+        <v>176.4</v>
+      </c>
+      <c r="I25">
+        <v>178.6</v>
+      </c>
+      <c r="J25">
+        <v>177.5</v>
+      </c>
+      <c r="K25">
+        <v>178.5</v>
+      </c>
+      <c r="L25">
+        <v>172.9</v>
+      </c>
+      <c r="M25">
+        <v>3.6</v>
+      </c>
+      <c r="N25">
+        <v>43.6</v>
+      </c>
+      <c r="O25">
+        <v>138.5</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>15</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-10-13 05:12:55.341</v>
+      </c>
+      <c r="C26">
+        <v>3.69</v>
+      </c>
+      <c r="D26" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E26" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F26" t="str">
+        <v>REP_COMPLETE</v>
+      </c>
+      <c r="G26">
+        <v>178</v>
+      </c>
+      <c r="H26">
+        <v>176.7</v>
+      </c>
+      <c r="I26">
+        <v>178.2</v>
+      </c>
+      <c r="J26">
+        <v>177.5</v>
+      </c>
+      <c r="K26">
+        <v>177.7</v>
+      </c>
+      <c r="L26">
+        <v>172.4</v>
+      </c>
+      <c r="M26">
+        <v>3.6</v>
+      </c>
+      <c r="N26">
+        <v>151.1</v>
+      </c>
+      <c r="O26">
+        <v>113.1</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>16</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-10-13 05:12:55.650</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E27" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F27" t="str">
+        <v>REP_COMPLETE</v>
+      </c>
+      <c r="G27">
+        <v>179</v>
+      </c>
+      <c r="H27">
+        <v>177.2</v>
+      </c>
+      <c r="I27">
+        <v>178.8</v>
+      </c>
+      <c r="J27">
+        <v>178</v>
+      </c>
+      <c r="K27">
+        <v>178.7</v>
+      </c>
+      <c r="L27">
+        <v>172.6</v>
+      </c>
+      <c r="M27">
+        <v>3.1</v>
+      </c>
+      <c r="N27">
+        <v>153.4</v>
+      </c>
+      <c r="O27">
+        <v>166.2</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>17</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-10-13 05:12:55.919</v>
+      </c>
+      <c r="C28">
+        <v>4.27</v>
+      </c>
+      <c r="D28" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E28" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F28" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G28">
+        <v>179</v>
+      </c>
+      <c r="H28">
+        <v>177.1</v>
+      </c>
+      <c r="I28">
+        <v>178.6</v>
+      </c>
+      <c r="J28">
+        <v>177.9</v>
+      </c>
+      <c r="K28">
+        <v>179</v>
+      </c>
+      <c r="L28">
+        <v>172.5</v>
+      </c>
+      <c r="M28">
+        <v>3</v>
+      </c>
+      <c r="N28">
+        <v>147.4</v>
+      </c>
+      <c r="O28">
+        <v>170.3</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>18</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-10-13 05:12:56.141</v>
+      </c>
+      <c r="C29">
+        <v>4.49</v>
+      </c>
+      <c r="D29" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E29" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F29" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G29">
+        <v>178</v>
+      </c>
+      <c r="H29">
+        <v>176.8</v>
+      </c>
+      <c r="I29">
+        <v>178.3</v>
+      </c>
+      <c r="J29">
+        <v>177.6</v>
+      </c>
+      <c r="K29">
+        <v>179.3</v>
+      </c>
+      <c r="L29">
+        <v>173</v>
+      </c>
+      <c r="M29">
+        <v>2.8</v>
+      </c>
+      <c r="N29">
+        <v>161</v>
+      </c>
+      <c r="O29">
+        <v>169.4</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>19</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-10-13 05:12:56.378</v>
+      </c>
+      <c r="C30">
+        <v>4.73</v>
+      </c>
+      <c r="D30" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E30" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F30" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G30">
+        <v>178</v>
+      </c>
+      <c r="H30">
+        <v>177.1</v>
+      </c>
+      <c r="I30">
+        <v>178.1</v>
+      </c>
+      <c r="J30">
+        <v>177.6</v>
+      </c>
+      <c r="K30">
+        <v>179.6</v>
+      </c>
+      <c r="L30">
+        <v>174.1</v>
+      </c>
+      <c r="M30">
+        <v>2.4</v>
+      </c>
+      <c r="N30">
+        <v>69.4</v>
+      </c>
+      <c r="O30">
+        <v>160.7</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>20</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-10-13 05:12:56.622</v>
+      </c>
+      <c r="C31">
+        <v>4.97</v>
+      </c>
+      <c r="D31" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E31" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F31" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G31">
+        <v>178</v>
+      </c>
+      <c r="H31">
+        <v>176.7</v>
+      </c>
+      <c r="I31">
+        <v>178</v>
+      </c>
+      <c r="J31">
+        <v>177.4</v>
+      </c>
+      <c r="K31">
+        <v>178.4</v>
+      </c>
+      <c r="L31">
+        <v>173.1</v>
+      </c>
+      <c r="M31">
+        <v>2.6</v>
+      </c>
+      <c r="N31">
+        <v>52.6</v>
+      </c>
+      <c r="O31">
+        <v>163.8</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>21</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-10-13 05:12:56.892</v>
+      </c>
+      <c r="C32">
+        <v>5.24</v>
+      </c>
+      <c r="D32" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E32" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F32" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G32">
+        <v>179</v>
+      </c>
+      <c r="H32">
+        <v>176</v>
+      </c>
+      <c r="I32">
+        <v>178.5</v>
+      </c>
+      <c r="J32">
+        <v>177.3</v>
+      </c>
+      <c r="K32">
+        <v>178.6</v>
+      </c>
+      <c r="L32">
+        <v>172.7</v>
+      </c>
+      <c r="M32">
+        <v>3.4</v>
+      </c>
+      <c r="N32">
+        <v>39.8</v>
+      </c>
+      <c r="O32">
+        <v>161.2</v>
+      </c>
+      <c r="P32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>22</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-10-13 05:12:57.103</v>
+      </c>
+      <c r="C33">
+        <v>5.45</v>
+      </c>
+      <c r="D33" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E33" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F33" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G33">
+        <v>178</v>
+      </c>
+      <c r="H33">
+        <v>175.8</v>
+      </c>
+      <c r="I33">
+        <v>178</v>
+      </c>
+      <c r="J33">
+        <v>176.9</v>
+      </c>
+      <c r="K33">
+        <v>178.7</v>
+      </c>
+      <c r="L33">
+        <v>172.9</v>
+      </c>
+      <c r="M33">
+        <v>3.3</v>
+      </c>
+      <c r="N33">
+        <v>33</v>
+      </c>
+      <c r="O33">
+        <v>150.2</v>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>23</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-10-13 05:12:57.429</v>
+      </c>
+      <c r="C34">
+        <v>5.78</v>
+      </c>
+      <c r="D34" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E34" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F34" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G34">
+        <v>178</v>
+      </c>
+      <c r="H34">
+        <v>176.5</v>
+      </c>
+      <c r="I34">
+        <v>178.4</v>
+      </c>
+      <c r="J34">
+        <v>177.5</v>
+      </c>
+      <c r="K34">
+        <v>178.3</v>
+      </c>
+      <c r="L34">
+        <v>172.4</v>
+      </c>
+      <c r="M34">
+        <v>4</v>
+      </c>
+      <c r="N34">
+        <v>29</v>
+      </c>
+      <c r="O34">
+        <v>155.8</v>
+      </c>
+      <c r="P34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>24</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-10-13 05:12:57.666</v>
+      </c>
+      <c r="C35">
+        <v>6.02</v>
+      </c>
+      <c r="D35" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E35" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F35" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G35">
+        <v>179</v>
+      </c>
+      <c r="H35">
+        <v>176.1</v>
+      </c>
+      <c r="I35">
+        <v>178.5</v>
+      </c>
+      <c r="J35">
+        <v>177.3</v>
+      </c>
+      <c r="K35">
+        <v>178.1</v>
+      </c>
+      <c r="L35">
+        <v>172.6</v>
+      </c>
+      <c r="M35">
+        <v>3.8</v>
+      </c>
+      <c r="N35">
+        <v>32.5</v>
+      </c>
+      <c r="O35">
+        <v>156.4</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>25</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-10-13 05:12:57.912</v>
+      </c>
+      <c r="C36">
+        <v>6.26</v>
+      </c>
+      <c r="D36" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E36" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F36" t="str">
+        <v>READY</v>
+      </c>
+      <c r="G36">
+        <v>178</v>
+      </c>
+      <c r="H36">
+        <v>176.5</v>
+      </c>
+      <c r="I36">
+        <v>178</v>
+      </c>
+      <c r="J36">
+        <v>177.3</v>
+      </c>
+      <c r="K36">
+        <v>178.4</v>
+      </c>
+      <c r="L36">
+        <v>173.3</v>
+      </c>
+      <c r="M36">
+        <v>2.6</v>
+      </c>
+      <c r="N36">
+        <v>132.3</v>
+      </c>
+      <c r="O36">
+        <v>163.7</v>
+      </c>
+      <c r="P36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>26</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-10-13 05:12:58.174</v>
+      </c>
+      <c r="C37">
+        <v>6.52</v>
+      </c>
+      <c r="D37" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E37" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F37" t="str">
+        <v>READY</v>
+      </c>
+      <c r="G37">
+        <v>178</v>
+      </c>
+      <c r="H37">
+        <v>177.3</v>
+      </c>
+      <c r="I37">
+        <v>178.2</v>
+      </c>
+      <c r="J37">
+        <v>177.8</v>
+      </c>
+      <c r="K37">
+        <v>179.6</v>
+      </c>
+      <c r="L37">
+        <v>173.9</v>
+      </c>
+      <c r="M37">
+        <v>2.2</v>
+      </c>
+      <c r="N37">
+        <v>150.3</v>
+      </c>
+      <c r="O37">
+        <v>167.4</v>
+      </c>
+      <c r="P37">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>27</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-10-13 05:12:58.436</v>
+      </c>
+      <c r="C38">
+        <v>6.79</v>
+      </c>
+      <c r="D38" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E38" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F38" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G38">
+        <v>178</v>
+      </c>
+      <c r="H38">
+        <v>177.2</v>
+      </c>
+      <c r="I38">
+        <v>178</v>
+      </c>
+      <c r="J38">
+        <v>177.6</v>
+      </c>
+      <c r="K38">
+        <v>179.9</v>
+      </c>
+      <c r="L38">
+        <v>173.7</v>
+      </c>
+      <c r="M38">
+        <v>2</v>
+      </c>
+      <c r="N38">
+        <v>149.6</v>
+      </c>
+      <c r="O38">
+        <v>164.2</v>
+      </c>
+      <c r="P38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>28</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-10-13 05:12:58.713</v>
+      </c>
+      <c r="C39">
+        <v>7.06</v>
+      </c>
+      <c r="D39" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E39" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F39" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G39">
+        <v>178</v>
+      </c>
+      <c r="H39">
+        <v>177.4</v>
+      </c>
+      <c r="I39">
+        <v>177.7</v>
+      </c>
+      <c r="J39">
+        <v>177.6</v>
+      </c>
+      <c r="K39">
+        <v>179.4</v>
+      </c>
+      <c r="L39">
+        <v>174.2</v>
+      </c>
+      <c r="M39">
+        <v>1.3</v>
+      </c>
+      <c r="N39">
+        <v>159.7</v>
+      </c>
+      <c r="O39">
+        <v>161.4</v>
+      </c>
+      <c r="P39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>29</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-10-13 05:12:58.975</v>
+      </c>
+      <c r="C40">
+        <v>7.33</v>
+      </c>
+      <c r="D40" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E40" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F40" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G40">
+        <v>178</v>
+      </c>
+      <c r="H40">
+        <v>176.8</v>
+      </c>
+      <c r="I40">
+        <v>177.9</v>
+      </c>
+      <c r="J40">
+        <v>177.4</v>
+      </c>
+      <c r="K40">
+        <v>179</v>
+      </c>
+      <c r="L40">
+        <v>174.4</v>
+      </c>
+      <c r="M40">
+        <v>1.1</v>
+      </c>
+      <c r="N40">
+        <v>170.6</v>
+      </c>
+      <c r="O40">
+        <v>159.3</v>
+      </c>
+      <c r="P40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>30</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-10-13 05:12:59.229</v>
+      </c>
+      <c r="C41">
+        <v>7.58</v>
+      </c>
+      <c r="D41" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E41" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F41" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G41">
+        <v>178</v>
+      </c>
+      <c r="H41">
+        <v>177.2</v>
+      </c>
+      <c r="I41">
+        <v>178.4</v>
+      </c>
+      <c r="J41">
+        <v>177.8</v>
+      </c>
+      <c r="K41">
+        <v>179.2</v>
+      </c>
+      <c r="L41">
+        <v>174.3</v>
+      </c>
+      <c r="M41">
+        <v>1.6</v>
+      </c>
+      <c r="N41">
+        <v>154.6</v>
+      </c>
+      <c r="O41">
+        <v>167.3</v>
+      </c>
+      <c r="P41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>31</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-10-13 05:12:59.466</v>
+      </c>
+      <c r="C42">
+        <v>7.82</v>
+      </c>
+      <c r="D42" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E42" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F42" t="str">
+        <v>IDLE</v>
+      </c>
+      <c r="G42">
+        <v>180</v>
+      </c>
+      <c r="H42">
+        <v>177.3</v>
+      </c>
+      <c r="I42">
+        <v>179.8</v>
+      </c>
+      <c r="J42">
+        <v>178.6</v>
+      </c>
+      <c r="K42">
+        <v>178.8</v>
+      </c>
+      <c r="L42">
+        <v>173.2</v>
+      </c>
+      <c r="M42">
+        <v>1.1</v>
+      </c>
+      <c r="N42">
+        <v>163.3</v>
+      </c>
+      <c r="O42">
+        <v>159.2</v>
+      </c>
+      <c r="P42">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>32</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-10-13 05:12:59.710</v>
+      </c>
+      <c r="C43">
+        <v>8.06</v>
+      </c>
+      <c r="D43" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E43" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F43" t="str">
+        <v>READY</v>
+      </c>
+      <c r="G43">
+        <v>179</v>
+      </c>
+      <c r="H43">
+        <v>177.9</v>
+      </c>
+      <c r="I43">
+        <v>179.3</v>
+      </c>
+      <c r="J43">
+        <v>178.6</v>
+      </c>
+      <c r="K43">
+        <v>177.1</v>
+      </c>
+      <c r="L43">
+        <v>173.4</v>
+      </c>
+      <c r="M43">
+        <v>1.2</v>
+      </c>
+      <c r="N43">
+        <v>145.3</v>
+      </c>
+      <c r="O43">
+        <v>168.3</v>
+      </c>
+      <c r="P43">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>33</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-10-13 05:13:00.000</v>
+      </c>
+      <c r="C44">
+        <v>8.35</v>
+      </c>
+      <c r="D44" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E44" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F44" t="str">
+        <v>DESCENDING</v>
+      </c>
+      <c r="G44">
+        <v>179</v>
+      </c>
+      <c r="H44">
+        <v>177.6</v>
+      </c>
+      <c r="I44">
+        <v>179</v>
+      </c>
+      <c r="J44">
+        <v>178.3</v>
+      </c>
+      <c r="K44">
+        <v>177.1</v>
+      </c>
+      <c r="L44">
+        <v>172.6</v>
+      </c>
+      <c r="M44">
+        <v>2.2</v>
+      </c>
+      <c r="N44">
+        <v>78.9</v>
+      </c>
+      <c r="O44">
+        <v>171.7</v>
+      </c>
+      <c r="P44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>34</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-10-13 05:13:00.266</v>
+      </c>
+      <c r="C45">
+        <v>8.62</v>
+      </c>
+      <c r="D45" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E45" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F45" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G45">
+        <v>179</v>
+      </c>
+      <c r="H45">
+        <v>177.5</v>
+      </c>
+      <c r="I45">
+        <v>178.6</v>
+      </c>
+      <c r="J45">
+        <v>178.1</v>
+      </c>
+      <c r="K45">
+        <v>177.6</v>
+      </c>
+      <c r="L45">
+        <v>173</v>
+      </c>
+      <c r="M45">
+        <v>2.1</v>
+      </c>
+      <c r="N45">
+        <v>54.3</v>
+      </c>
+      <c r="O45">
+        <v>170.2</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>35</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-10-13 05:13:00.477</v>
+      </c>
+      <c r="C46">
+        <v>8.83</v>
+      </c>
+      <c r="D46" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E46" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F46" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G46">
+        <v>179</v>
+      </c>
+      <c r="H46">
+        <v>176.5</v>
+      </c>
+      <c r="I46">
+        <v>179.4</v>
+      </c>
+      <c r="J46">
+        <v>178</v>
+      </c>
+      <c r="K46">
+        <v>177.8</v>
+      </c>
+      <c r="L46">
+        <v>173.1</v>
+      </c>
+      <c r="M46">
+        <v>2</v>
+      </c>
+      <c r="N46">
+        <v>42</v>
+      </c>
+      <c r="O46">
+        <v>162</v>
+      </c>
+      <c r="P46">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>36</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-10-13 05:13:00.686</v>
+      </c>
+      <c r="C47">
+        <v>9.04</v>
+      </c>
+      <c r="D47" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E47" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F47" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G47">
+        <v>179</v>
+      </c>
+      <c r="H47">
+        <v>177</v>
+      </c>
+      <c r="I47">
+        <v>179</v>
+      </c>
+      <c r="J47">
+        <v>178</v>
+      </c>
+      <c r="K47">
+        <v>177.7</v>
+      </c>
+      <c r="L47">
+        <v>173.3</v>
+      </c>
+      <c r="M47">
+        <v>1.8</v>
+      </c>
+      <c r="N47">
+        <v>37.3</v>
+      </c>
+      <c r="O47">
+        <v>162.3</v>
+      </c>
+      <c r="P47">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>37</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-10-13 05:13:00.923</v>
+      </c>
+      <c r="C48">
+        <v>9.27</v>
+      </c>
+      <c r="D48" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E48" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F48" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G48">
+        <v>179</v>
+      </c>
+      <c r="H48">
+        <v>176.7</v>
+      </c>
+      <c r="I48">
+        <v>179.3</v>
+      </c>
+      <c r="J48">
+        <v>178</v>
+      </c>
+      <c r="K48">
+        <v>177.9</v>
+      </c>
+      <c r="L48">
+        <v>173.1</v>
+      </c>
+      <c r="M48">
+        <v>1.1</v>
+      </c>
+      <c r="N48">
+        <v>35.7</v>
+      </c>
+      <c r="O48">
+        <v>150.2</v>
+      </c>
+      <c r="P48">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>38</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-10-13 05:13:01.176</v>
+      </c>
+      <c r="C49">
+        <v>9.53</v>
+      </c>
+      <c r="D49" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E49" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F49" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G49">
+        <v>179</v>
+      </c>
+      <c r="H49">
+        <v>177</v>
+      </c>
+      <c r="I49">
+        <v>178.8</v>
+      </c>
+      <c r="J49">
+        <v>177.9</v>
+      </c>
+      <c r="K49">
+        <v>178.8</v>
+      </c>
+      <c r="L49">
+        <v>173.8</v>
+      </c>
+      <c r="M49">
+        <v>1.7</v>
+      </c>
+      <c r="N49">
+        <v>33.3</v>
+      </c>
+      <c r="O49">
+        <v>161.9</v>
+      </c>
+      <c r="P49">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>39</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-10-13 05:13:01.387</v>
+      </c>
+      <c r="C50">
+        <v>9.74</v>
+      </c>
+      <c r="D50" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E50" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F50" t="str">
+        <v>BOTTOM</v>
+      </c>
+      <c r="G50">
+        <v>178</v>
+      </c>
+      <c r="H50">
+        <v>176.4</v>
+      </c>
+      <c r="I50">
+        <v>177.9</v>
+      </c>
+      <c r="J50">
+        <v>177.2</v>
+      </c>
+      <c r="K50">
+        <v>179.7</v>
+      </c>
+      <c r="L50">
+        <v>174.6</v>
+      </c>
+      <c r="M50">
+        <v>1.7</v>
+      </c>
+      <c r="N50">
+        <v>55.4</v>
+      </c>
+      <c r="O50">
+        <v>157.5</v>
+      </c>
+      <c r="P50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>40</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-10-13 05:13:01.624</v>
+      </c>
+      <c r="C51">
+        <v>9.97</v>
+      </c>
+      <c r="D51" t="str">
+        <v>ses_mv685waq_17nl</v>
+      </c>
+      <c r="E51" t="str">
+        <v>arm_curl</v>
+      </c>
+      <c r="F51" t="str">
+        <v>REP_COMPLETE</v>
+      </c>
+      <c r="G51">
+        <v>179</v>
+      </c>
+      <c r="H51">
+        <v>176.9</v>
+      </c>
+      <c r="I51">
+        <v>178.6</v>
+      </c>
+      <c r="J51">
+        <v>177.8</v>
+      </c>
+      <c r="K51">
+        <v>179.7</v>
+      </c>
+      <c r="L51">
+        <v>174.4</v>
+      </c>
+      <c r="M51">
+        <v>1.6</v>
+      </c>
+      <c r="N51">
+        <v>156.7</v>
+      </c>
+      <c r="O51">
+        <v>157.2</v>
+      </c>
+      <c r="P51">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P51"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1061,16 +5331,16 @@
         <v>Rep_ID</v>
       </c>
       <c r="C2" t="str">
-        <v>String</v>
+        <v>String (UUID)</v>
       </c>
       <c r="D2" t="str">
         <v>Identifier</v>
       </c>
       <c r="E2" t="str">
-        <v>Unique repetition identifier</v>
+        <v>Unique repetition identifier format: rep_{exercise}_{repNum}_{timestamp}</v>
       </c>
       <c r="F2" t="str">
-        <v>Primary key for relational joins</v>
+        <v>Primary key for relational linking to telemetry frames.</v>
       </c>
     </row>
     <row r="3">
@@ -1078,19 +5348,19 @@
         <v>Repetitions</v>
       </c>
       <c r="B3" t="str">
-        <v>Peak_Flexion_Deg</v>
+        <v>Form_Result</v>
       </c>
       <c r="C3" t="str">
-        <v>Float</v>
+        <v>Categorical</v>
       </c>
       <c r="D3" t="str">
-        <v>Degrees (°)</v>
+        <v>PASS / FAIL</v>
       </c>
       <c r="E3" t="str">
-        <v>Minimum interior joint angle achieved at lowest descent or maximum contraction</v>
+        <v>Clinical pass/fail label based on depth criteria and spine posture safety.</v>
       </c>
       <c r="F3" t="str">
-        <v>Lower angle indicates greater joint flexion and depth</v>
+        <v>PASS indicates full biomechanical range of motion without posture violation.</v>
       </c>
     </row>
     <row r="4">
@@ -1098,19 +5368,19 @@
         <v>Repetitions</v>
       </c>
       <c r="B4" t="str">
-        <v>Range_Of_Motion_Deg</v>
+        <v>Is_Valid</v>
       </c>
       <c r="C4" t="str">
-        <v>Float</v>
+        <v>Integer Binary</v>
       </c>
       <c r="D4" t="str">
-        <v>Degrees (°)</v>
+        <v>1 or 0</v>
       </c>
       <c r="E4" t="str">
-        <v>Angular displacement from initial standing position to peak bottom flexion</v>
+        <v>Binary target label for Machine Learning classification models (1 = Valid, 0 = Fault).</v>
       </c>
       <c r="F4" t="str">
-        <v>Indicates total mechanical work and mobility across the joint</v>
+        <v>Direct target variable for training ML form classifiers.</v>
       </c>
     </row>
     <row r="5">
@@ -1118,7 +5388,7 @@
         <v>Repetitions</v>
       </c>
       <c r="B5" t="str">
-        <v>Knee_Asymmetry_Deg</v>
+        <v>Target_Threshold_Deg</v>
       </c>
       <c r="C5" t="str">
         <v>Float</v>
@@ -1127,10 +5397,10 @@
         <v>Degrees (°)</v>
       </c>
       <c r="E5" t="str">
-        <v>|Left_Knee_Min_Deg - Right_Knee_Min_Deg|</v>
+        <v>Prescribed joint angle threshold required for exercise completion.</v>
       </c>
       <c r="F5" t="str">
-        <v>&gt; 15° indicates significant bilateral weight-shift or unilateral muscle weakness</v>
+        <v>Gentle: 125°, Standard: 105°, Deep athletic: 90° for squats.</v>
       </c>
     </row>
     <row r="6">
@@ -1138,7 +5408,7 @@
         <v>Repetitions</v>
       </c>
       <c r="B6" t="str">
-        <v>Max_Torso_Lean_Deg</v>
+        <v>Peak_Flexion_Deg</v>
       </c>
       <c r="C6" t="str">
         <v>Float</v>
@@ -1147,10 +5417,10 @@
         <v>Degrees (°)</v>
       </c>
       <c r="E6" t="str">
-        <v>Angle between vector (Hip Midpoint to Shoulder Midpoint) and vertical axis</v>
+        <v>Minimum interior joint angle achieved at lowest descent or maximum contraction.</v>
       </c>
       <c r="F6" t="str">
-        <v>&gt; 35° indicates excessive forward spinal shear and insufficient core engagement</v>
+        <v>Lower angle indicates greater joint flexion and depth.</v>
       </c>
     </row>
     <row r="7">
@@ -1158,24 +5428,184 @@
         <v>Repetitions</v>
       </c>
       <c r="B7" t="str">
-        <v>Avg_Angular_Velocity_DegSec</v>
+        <v>Range_Of_Motion_Deg</v>
       </c>
       <c r="C7" t="str">
         <v>Float</v>
       </c>
       <c r="D7" t="str">
+        <v>Degrees (°)</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Angular displacement from initial standing position to peak bottom flexion.</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Indicates total mechanical work and mobility across the joint.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Repetitions</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Threshold_Margin_Deg</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Float</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Degrees (°)</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Target_Threshold_Deg minus Peak_Flexion_Deg.</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Positive values indicate depth exceeded target. Negative values indicate shallow reps.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Repetitions</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Knee_Asymmetry_Deg</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Float</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Degrees (°)</v>
+      </c>
+      <c r="E9" t="str">
+        <v>|Left_Knee_Min_Deg - Right_Knee_Min_Deg|.</v>
+      </c>
+      <c r="F9" t="str">
+        <v>&gt; 15° indicates significant bilateral weight-shift or unilateral muscle weakness.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Repetitions</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Max_Torso_Lean_Deg</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Float</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Degrees (°)</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Angle between vector (Hip Midpoint to Shoulder Midpoint) and vertical axis (0° = upright).</v>
+      </c>
+      <c r="F10" t="str">
+        <v>&gt; 35° indicates excessive forward spinal shear and insufficient core engagement.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Repetitions</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Eccentric_Phase_Sec</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Float</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Seconds (s)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Duration from descent initiation to lowest peak flexion point.</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Controlled lowering (tempo 2.0-3.0s) reduces patellar strain.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Repetitions</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Concentric_Phase_Sec</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Float</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Seconds (s)</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Duration from lowest peak flexion point back to full standing lockout.</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Measures concentric rate of force development.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Repetitions</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Avg_Angular_Velocity_DegSec</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Float</v>
+      </c>
+      <c r="D13" t="str">
         <v>°/s</v>
       </c>
-      <c r="E7" t="str">
-        <v>Range of Motion divided by Total Repetition Duration</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Biomechanical speed of joint rotation during repetition</v>
+      <c r="E13" t="str">
+        <v>Range of Motion divided by Total Repetition Duration.</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Biomechanical speed of joint rotation during repetition.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Kinematics_Telemetry</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Mean_Knee_Deg</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Float</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Degrees (°)</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Bilateral mean of left and right knee interior angles formed by Hip-Knee-Ankle.</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Continuous time-series variable for trajectory modeling and phase segmentation.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Kinematics_Telemetry</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Torso_Lean_Deg</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Float</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Degrees (°)</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Continuous sagittal inclination of the spine relative to vertical gravity vector.</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Dynamic lumbar-pelvic rhythm marker during exercise cycles.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
   </ignoredErrors>
 </worksheet>
 </file>